--- a/Documents/Prouct_List.xlsx
+++ b/Documents/Prouct_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SuperCRM\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F885E-7A2B-4B17-BE1C-64E2CC6711EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260EDF44-627F-4E29-854C-23903C8513BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="6480" xr2:uid="{58D52B7B-F928-43CB-8F7E-2DF445B605F6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="117">
   <si>
     <t>CategoryName</t>
   </si>
@@ -63,9 +63,6 @@
     <t>CurrencyCode</t>
   </si>
   <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
     <t>DownPaymentAmount</t>
   </si>
   <si>
@@ -138,27 +135,9 @@
     <t>Card machine( One-off )</t>
   </si>
   <si>
-    <t>Installment Amount: £15/month</t>
-  </si>
-  <si>
-    <t>CARD-MACH-VIVA-PKG1</t>
-  </si>
-  <si>
-    <t>Card machine ViVa(Package1)</t>
-  </si>
-  <si>
-    <t>Installment Amount: £12/month</t>
-  </si>
-  <si>
     <t>Contract Period: 18 Months, Installment Amount: 12</t>
   </si>
   <si>
-    <t>CARD-MACH-VIVA-PKG2</t>
-  </si>
-  <si>
-    <t>Card machine Viva(Package2)</t>
-  </si>
-  <si>
     <t>One-off -&gt; Starts from £250</t>
   </si>
   <si>
@@ -339,9 +318,6 @@
     <t>SIM RESIDENTIAL</t>
   </si>
   <si>
-    <t>Per Year</t>
-  </si>
-  <si>
     <t>RES-TELEPHONE</t>
   </si>
   <si>
@@ -363,17 +339,50 @@
     <t>Both</t>
   </si>
   <si>
-    <t>Is Installment/Monthly Payment Applicable</t>
-  </si>
-  <si>
     <t>Monthly Installment Amount</t>
+  </si>
+  <si>
+    <t>Unit Price as Sales Unit</t>
+  </si>
+  <si>
+    <t>Is Installment Applicable</t>
+  </si>
+  <si>
+    <t>Monthly Amount: £15/month</t>
+  </si>
+  <si>
+    <t>CARD-MACH-TEYA-PKG1</t>
+  </si>
+  <si>
+    <t>Card machine Teya(Package1)</t>
+  </si>
+  <si>
+    <t>Monthly Amount: £15/month(debit and credit cards charge 1% blended)</t>
+  </si>
+  <si>
+    <t>Contract Period: 12 Months, Installment Amount: £15 + VAT</t>
+  </si>
+  <si>
+    <t>CARD-MACH-TEYA-PKG2</t>
+  </si>
+  <si>
+    <t>Card machine Teya(Package2)</t>
+  </si>
+  <si>
+    <t>One-off -&gt; Fixed £150</t>
+  </si>
+  <si>
+    <t>Minimum usages contract six month.</t>
+  </si>
+  <si>
+    <t>Monthly Amount: £12/month</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,13 +390,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -417,9 +440,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,7 +773,8 @@
     <col min="10" max="10" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.36328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.90625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25.1796875" bestFit="1" customWidth="1"/>
@@ -763,119 +788,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -887,19 +912,19 @@
         <v>0</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W2" s="1">
         <v>1</v>
@@ -908,42 +933,42 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="M3" s="1">
         <v>15</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
@@ -955,19 +980,19 @@
         <v>0</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W3" s="1">
         <v>5</v>
@@ -976,44 +1001,44 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="M4" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
@@ -1025,19 +1050,19 @@
         <v>0</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W4" s="1">
         <v>20</v>
@@ -1046,42 +1071,44 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="J5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M5" s="1">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -1093,19 +1120,19 @@
         <v>0</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W5" s="1">
         <v>25</v>
@@ -1114,44 +1141,44 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="M6" s="1">
         <v>12</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -1163,19 +1190,19 @@
         <v>0</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W6" s="1">
         <v>30</v>
@@ -1184,42 +1211,42 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M7" s="1">
         <v>250</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -1231,19 +1258,19 @@
         <v>0</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W7" s="1">
         <v>34</v>
@@ -1252,42 +1279,42 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="J8" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M8" s="1">
         <v>0</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O8" s="1">
         <v>0</v>
@@ -1299,19 +1326,19 @@
         <v>0</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -1320,42 +1347,42 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -1367,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W9" s="1">
         <v>3</v>
@@ -1388,42 +1415,42 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M10" s="1">
         <v>750</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="1">
         <v>300</v>
@@ -1435,63 +1462,63 @@
         <v>50</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -1503,19 +1530,19 @@
         <v>0</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W11" s="1">
         <v>50</v>
@@ -1524,42 +1551,42 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M12" s="1">
         <v>399</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12" s="1">
         <v>99</v>
@@ -1571,67 +1598,67 @@
         <v>50</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W12" s="1">
         <v>60</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M13" s="1">
         <v>399</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O13" s="1">
         <v>199</v>
@@ -1640,22 +1667,22 @@
         <v>4</v>
       </c>
       <c r="Q13" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W13" s="1">
         <v>70</v>
@@ -1664,42 +1691,42 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M14" s="1">
         <v>250</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O14" s="1">
         <v>100</v>
@@ -1711,19 +1738,19 @@
         <v>50</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W14" s="1">
         <v>80</v>
@@ -1732,42 +1759,42 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M15" s="1">
         <v>300</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O15" s="1">
         <v>100</v>
@@ -1779,19 +1806,19 @@
         <v>50</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W15" s="1">
         <v>90</v>
@@ -1800,42 +1827,42 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -1847,19 +1874,19 @@
         <v>0</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W16" s="1">
         <v>100</v>
@@ -1868,42 +1895,42 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="J17" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="M17" s="1">
         <v>0</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
@@ -1915,19 +1942,19 @@
         <v>0</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W17" s="1">
         <v>0</v>
@@ -1936,42 +1963,42 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="J18" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="M18" s="1">
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -1983,19 +2010,19 @@
         <v>0</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W18" s="1">
         <v>0</v>
@@ -2004,42 +2031,42 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M19" s="1">
         <v>0</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -2051,19 +2078,19 @@
         <v>0</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W19" s="1">
         <v>0</v>
@@ -2072,42 +2099,42 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -2119,19 +2146,19 @@
         <v>0</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W20" s="1">
         <v>120</v>
@@ -2140,40 +2167,40 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M21" s="1">
         <v>20</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -2185,19 +2212,19 @@
         <v>0</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W21" s="1">
         <v>0</v>
@@ -2206,40 +2233,40 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="M22" s="1">
         <v>20</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -2251,19 +2278,19 @@
         <v>0</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W22" s="1">
         <v>0</v>
@@ -2272,40 +2299,40 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="M23" s="1">
         <v>20</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -2317,19 +2344,19 @@
         <v>0</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W23" s="1">
         <v>139</v>
@@ -2338,5 +2365,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>